--- a/data/dental_clinic_database.xlsx
+++ b/data/dental_clinic_database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -438,22 +438,22 @@
         <v>Kamal Perera</v>
       </c>
       <c r="C2" t="str">
-        <v>0771234567</v>
+        <v>0763182332</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E2" t="str">
         <v>Male</v>
       </c>
       <c r="F2" t="str">
-        <v>Matara</v>
+        <v>Kandy</v>
       </c>
       <c r="G2">
         <v>46199.375</v>
       </c>
-      <c r="H2" t="str">
-        <v>2026-06-27T16:17:35.508Z</v>
+      <c r="H2">
+        <v>46199.375</v>
       </c>
     </row>
     <row r="3">
@@ -464,10 +464,10 @@
         <v>Nimali Fernando</v>
       </c>
       <c r="C3" t="str">
-        <v>0712345678</v>
+        <v>0737058601</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E3" t="str">
         <v>Female</v>
@@ -487,25 +487,19 @@
         <v>PAT_0003</v>
       </c>
       <c r="B4" t="str">
-        <v>Sunil Jayawardena</v>
-      </c>
-      <c r="C4">
-        <v>761234567</v>
+        <v>Saman Silva</v>
+      </c>
+      <c r="C4" t="str">
+        <v>0707053081</v>
       </c>
       <c r="D4">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="E4" t="str">
         <v>Male</v>
       </c>
       <c r="F4" t="str">
-        <v>Galle</v>
-      </c>
-      <c r="G4">
-        <v>46199.38</v>
-      </c>
-      <c r="H4">
-        <v>46199.38</v>
+        <v>Kandy</v>
       </c>
     </row>
     <row r="5">
@@ -513,25 +507,19 @@
         <v>PAT_0004</v>
       </c>
       <c r="B5" t="str">
-        <v>Shanika Silva</v>
-      </c>
-      <c r="C5">
-        <v>752345678</v>
+        <v>Dilani Jayasinghe</v>
+      </c>
+      <c r="C5" t="str">
+        <v>0725621873</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E5" t="str">
         <v>Female</v>
       </c>
       <c r="F5" t="str">
         <v>Matara</v>
-      </c>
-      <c r="G5">
-        <v>46199.381</v>
-      </c>
-      <c r="H5">
-        <v>46199.381</v>
       </c>
     </row>
     <row r="6">
@@ -539,25 +527,19 @@
         <v>PAT_0005</v>
       </c>
       <c r="B6" t="str">
-        <v>Ruwan Perera</v>
-      </c>
-      <c r="C6">
-        <v>783456789</v>
+        <v>Ruwan Fernando</v>
+      </c>
+      <c r="C6" t="str">
+        <v>0793514909</v>
       </c>
       <c r="D6">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="E6" t="str">
         <v>Male</v>
       </c>
       <c r="F6" t="str">
-        <v>Kandy</v>
-      </c>
-      <c r="G6">
-        <v>46199.382</v>
-      </c>
-      <c r="H6">
-        <v>46199.382</v>
+        <v>Negombo</v>
       </c>
     </row>
     <row r="7">
@@ -565,25 +547,19 @@
         <v>PAT_0006</v>
       </c>
       <c r="B7" t="str">
-        <v>Dilani Gunasekara</v>
-      </c>
-      <c r="C7">
-        <v>704567891</v>
+        <v>Hasini Perera</v>
+      </c>
+      <c r="C7" t="str">
+        <v>0721677012</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="E7" t="str">
         <v>Female</v>
       </c>
       <c r="F7" t="str">
-        <v>Negombo</v>
-      </c>
-      <c r="G7">
-        <v>46199.383</v>
-      </c>
-      <c r="H7">
-        <v>46199.383</v>
+        <v>Colombo</v>
       </c>
     </row>
     <row r="8">
@@ -591,25 +567,19 @@
         <v>PAT_0007</v>
       </c>
       <c r="B8" t="str">
-        <v>Kasun Wijesinghe</v>
-      </c>
-      <c r="C8">
-        <v>745678912</v>
+        <v>Tharindu Lakmal</v>
+      </c>
+      <c r="C8" t="str">
+        <v>0727950093</v>
       </c>
       <c r="D8">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E8" t="str">
         <v>Male</v>
       </c>
       <c r="F8" t="str">
-        <v>Hambantota</v>
-      </c>
-      <c r="G8">
-        <v>46199.384</v>
-      </c>
-      <c r="H8">
-        <v>46199.384</v>
+        <v>Kandy</v>
       </c>
     </row>
     <row r="9">
@@ -617,25 +587,19 @@
         <v>PAT_0008</v>
       </c>
       <c r="B9" t="str">
-        <v>Anusha Karunaratne</v>
-      </c>
-      <c r="C9">
-        <v>776789123</v>
+        <v>Iresha Kumari</v>
+      </c>
+      <c r="C9" t="str">
+        <v>0745659143</v>
       </c>
       <c r="D9">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E9" t="str">
         <v>Female</v>
       </c>
       <c r="F9" t="str">
-        <v>Gampaha</v>
-      </c>
-      <c r="G9">
-        <v>46199.385</v>
-      </c>
-      <c r="H9">
-        <v>46199.385</v>
+        <v>Colombo</v>
       </c>
     </row>
     <row r="10">
@@ -643,25 +607,19 @@
         <v>PAT_0009</v>
       </c>
       <c r="B10" t="str">
-        <v>Nuwan Rathnayake</v>
-      </c>
-      <c r="C10">
-        <v>717891234</v>
+        <v>Kasun Madushanka</v>
+      </c>
+      <c r="C10" t="str">
+        <v>0756705401</v>
       </c>
       <c r="D10">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E10" t="str">
         <v>Male</v>
       </c>
       <c r="F10" t="str">
-        <v>Kurunegala</v>
-      </c>
-      <c r="G10">
-        <v>46199.386</v>
-      </c>
-      <c r="H10">
-        <v>46199.386</v>
+        <v>Kandy</v>
       </c>
     </row>
     <row r="11">
@@ -669,25 +627,19 @@
         <v>PAT_0010</v>
       </c>
       <c r="B11" t="str">
-        <v>Sanduni Perera</v>
-      </c>
-      <c r="C11">
-        <v>758912345</v>
+        <v>Sachini Silva</v>
+      </c>
+      <c r="C11" t="str">
+        <v>0708061933</v>
       </c>
       <c r="D11">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E11" t="str">
         <v>Female</v>
       </c>
       <c r="F11" t="str">
-        <v>Panadura</v>
-      </c>
-      <c r="G11">
-        <v>46199.387</v>
-      </c>
-      <c r="H11">
-        <v>46199.387</v>
+        <v>Matara</v>
       </c>
     </row>
     <row r="12">
@@ -695,25 +647,19 @@
         <v>PAT_0011</v>
       </c>
       <c r="B12" t="str">
-        <v>Chathura De Silva</v>
-      </c>
-      <c r="C12">
-        <v>769123456</v>
+        <v>Dinesh Perera</v>
+      </c>
+      <c r="C12" t="str">
+        <v>0727457392</v>
       </c>
       <c r="D12">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="E12" t="str">
         <v>Male</v>
       </c>
       <c r="F12" t="str">
-        <v>Kalutara</v>
-      </c>
-      <c r="G12">
-        <v>46199.388</v>
-      </c>
-      <c r="H12">
-        <v>46199.388</v>
+        <v>Colombo</v>
       </c>
     </row>
     <row r="13">
@@ -721,25 +667,19 @@
         <v>PAT_0012</v>
       </c>
       <c r="B13" t="str">
-        <v>Ishara Fernando</v>
-      </c>
-      <c r="C13">
-        <v>781239876</v>
+        <v>Upeksha Fernando</v>
+      </c>
+      <c r="C13" t="str">
+        <v>0711866007</v>
       </c>
       <c r="D13">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E13" t="str">
         <v>Female</v>
       </c>
       <c r="F13" t="str">
         <v>Galle</v>
-      </c>
-      <c r="G13">
-        <v>46199.389</v>
-      </c>
-      <c r="H13">
-        <v>46199.389</v>
       </c>
     </row>
     <row r="14">
@@ -747,25 +687,19 @@
         <v>PAT_0013</v>
       </c>
       <c r="B14" t="str">
-        <v>Tharindu Samarasinghe</v>
-      </c>
-      <c r="C14">
-        <v>702345678</v>
+        <v>Ashan Wickrama</v>
+      </c>
+      <c r="C14" t="str">
+        <v>0712243070</v>
       </c>
       <c r="D14">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="E14" t="str">
         <v>Male</v>
       </c>
       <c r="F14" t="str">
-        <v>Anuradhapura</v>
-      </c>
-      <c r="G14">
-        <v>46199.39</v>
-      </c>
-      <c r="H14">
-        <v>46199.39</v>
+        <v>Galle</v>
       </c>
     </row>
     <row r="15">
@@ -773,25 +707,19 @@
         <v>PAT_0014</v>
       </c>
       <c r="B15" t="str">
-        <v>Hashini Wickramasinghe</v>
-      </c>
-      <c r="C15">
-        <v>743456789</v>
+        <v>Nadeesha Perera</v>
+      </c>
+      <c r="C15" t="str">
+        <v>0793389857</v>
       </c>
       <c r="D15">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E15" t="str">
         <v>Female</v>
       </c>
       <c r="F15" t="str">
-        <v>Matale</v>
-      </c>
-      <c r="G15">
-        <v>46199.391</v>
-      </c>
-      <c r="H15">
-        <v>46199.391</v>
+        <v>Colombo</v>
       </c>
     </row>
     <row r="16">
@@ -799,25 +727,19 @@
         <v>PAT_0015</v>
       </c>
       <c r="B16" t="str">
-        <v>Pradeep Kumara</v>
-      </c>
-      <c r="C16">
-        <v>714567890</v>
+        <v>Gayan Silva</v>
+      </c>
+      <c r="C16" t="str">
+        <v>0783115010</v>
       </c>
       <c r="D16">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E16" t="str">
         <v>Male</v>
       </c>
       <c r="F16" t="str">
-        <v>Badulla</v>
-      </c>
-      <c r="G16">
-        <v>46199.392</v>
-      </c>
-      <c r="H16">
-        <v>46199.392</v>
+        <v>Galle</v>
       </c>
     </row>
     <row r="17">
@@ -825,25 +747,19 @@
         <v>PAT_0016</v>
       </c>
       <c r="B17" t="str">
-        <v>Sachini Madushani</v>
-      </c>
-      <c r="C17">
-        <v>755678901</v>
+        <v>Piumi Senanayake</v>
+      </c>
+      <c r="C17" t="str">
+        <v>0709153594</v>
       </c>
       <c r="D17">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E17" t="str">
         <v>Female</v>
       </c>
       <c r="F17" t="str">
-        <v>Ratnapura</v>
-      </c>
-      <c r="G17">
-        <v>46199.393</v>
-      </c>
-      <c r="H17">
-        <v>46199.393</v>
+        <v>Kandy</v>
       </c>
     </row>
     <row r="18">
@@ -851,25 +767,19 @@
         <v>PAT_0017</v>
       </c>
       <c r="B18" t="str">
-        <v>Lahiru Senanayake</v>
-      </c>
-      <c r="C18">
-        <v>776789012</v>
+        <v>Charith Perera</v>
+      </c>
+      <c r="C18" t="str">
+        <v>0746920781</v>
       </c>
       <c r="D18">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="E18" t="str">
         <v>Male</v>
       </c>
       <c r="F18" t="str">
-        <v>Colombo</v>
-      </c>
-      <c r="G18">
-        <v>46199.394</v>
-      </c>
-      <c r="H18">
-        <v>46199.394</v>
+        <v>Galle</v>
       </c>
     </row>
     <row r="19">
@@ -877,25 +787,19 @@
         <v>PAT_0018</v>
       </c>
       <c r="B19" t="str">
-        <v>Upeksha Ekanayake</v>
-      </c>
-      <c r="C19">
-        <v>787890123</v>
+        <v>Thilini Fernando</v>
+      </c>
+      <c r="C19" t="str">
+        <v>0799986814</v>
       </c>
       <c r="D19">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="E19" t="str">
         <v>Female</v>
       </c>
       <c r="F19" t="str">
-        <v>Kegalle</v>
-      </c>
-      <c r="G19">
-        <v>46199.395</v>
-      </c>
-      <c r="H19">
-        <v>46199.395</v>
+        <v>Negombo</v>
       </c>
     </row>
     <row r="20">
@@ -903,25 +807,19 @@
         <v>PAT_0019</v>
       </c>
       <c r="B20" t="str">
-        <v>Dinesh Abeykoon</v>
-      </c>
-      <c r="C20">
-        <v>708901234</v>
+        <v>Rashmi Perera</v>
+      </c>
+      <c r="C20" t="str">
+        <v>0786159243</v>
       </c>
       <c r="D20">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="E20" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="F20" t="str">
-        <v>Monaragala</v>
-      </c>
-      <c r="G20">
-        <v>46199.396</v>
-      </c>
-      <c r="H20">
-        <v>46199.396</v>
+        <v>Galle</v>
       </c>
     </row>
     <row r="21">
@@ -929,89 +827,32 @@
         <v>PAT_0020</v>
       </c>
       <c r="B21" t="str">
-        <v>Piumi Rajapaksha</v>
-      </c>
-      <c r="C21">
-        <v>719012345</v>
+        <v>Supun Silva</v>
+      </c>
+      <c r="C21" t="str">
+        <v>0757024761</v>
       </c>
       <c r="D21">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="E21" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="F21" t="str">
-        <v>Matara</v>
-      </c>
-      <c r="G21">
-        <v>46199.397</v>
-      </c>
-      <c r="H21">
-        <v>46199.397</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>PAT_844afc22</v>
-      </c>
-      <c r="B22" t="str">
-        <v>Chamika</v>
-      </c>
-      <c r="C22" t="str">
-        <v>0771234567</v>
-      </c>
-      <c r="D22" t="str">
-        <v/>
-      </c>
-      <c r="E22" t="str">
-        <v>Male</v>
-      </c>
-      <c r="F22" t="str">
-        <v/>
-      </c>
-      <c r="G22" t="str">
-        <v>2026-06-27T17:03:39.390Z</v>
-      </c>
-      <c r="H22" t="str">
-        <v>2026-06-27T17:03:39.390Z</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>PAT_fde18ed7</v>
-      </c>
-      <c r="B23" t="str">
-        <v>Chamika</v>
-      </c>
-      <c r="C23" t="str">
-        <v>0771234567</v>
-      </c>
-      <c r="D23" t="str">
-        <v>1234</v>
-      </c>
-      <c r="E23" t="str">
-        <v>Male</v>
-      </c>
-      <c r="F23" t="str">
-        <v/>
-      </c>
-      <c r="G23" t="str">
-        <v>2026-06-27T17:28:07.097Z</v>
-      </c>
-      <c r="H23" t="str">
-        <v>2026-06-27T17:28:07.097Z</v>
+        <v>Colombo</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H21"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1049,40 +890,21 @@
       <c r="E2">
         <v>46199.354166666664</v>
       </c>
-      <c r="F2" t="str">
-        <v>2026-06-27T16:19:51.092Z</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>DEN_0002</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Dr. Malini Perera</v>
-      </c>
-      <c r="C3" t="str">
-        <v>0726666666</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Orthodontics</v>
-      </c>
-      <c r="E3">
-        <v>46199.35763888889</v>
-      </c>
-      <c r="F3">
-        <v>46199.35763888889</v>
+      <c r="F2">
+        <v>46199.354166666664</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1124,22 +946,22 @@
         <v>DEN_0001</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-27</v>
+        <v>2026-06-26</v>
       </c>
       <c r="E2" t="str">
-        <v>21:51</v>
+        <v>10:00</v>
       </c>
       <c r="F2" t="str">
-        <v>Tooth Pain</v>
+        <v>Tooth pain</v>
       </c>
       <c r="G2" t="str">
         <v>Completed</v>
       </c>
-      <c r="H2" t="str">
-        <v>2026-06-27T16:21:49.356Z</v>
-      </c>
-      <c r="I2" t="str">
-        <v>2026-06-27T17:07:17.211Z</v>
+      <c r="H2">
+        <v>46199.395833333336</v>
+      </c>
+      <c r="I2">
+        <v>46199.458333333336</v>
       </c>
     </row>
     <row r="3">
@@ -1147,28 +969,28 @@
         <v>APP_0002</v>
       </c>
       <c r="B3" t="str">
-        <v>PAT_0008</v>
+        <v>PAT_0002</v>
       </c>
       <c r="C3" t="str">
-        <v>DEN_0001</v>
+        <v>DEN_0002</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-06-27</v>
+        <v>2026-06-26</v>
       </c>
       <c r="E3" t="str">
-        <v>21:53</v>
+        <v>11:00</v>
       </c>
       <c r="F3" t="str">
-        <v>Tooth Pain</v>
+        <v>Braces consultation</v>
       </c>
       <c r="G3" t="str">
-        <v>Cancelled</v>
-      </c>
-      <c r="H3" t="str">
-        <v>2026-06-27T16:24:00.210Z</v>
-      </c>
-      <c r="I3" t="str">
-        <v>2026-06-27T17:05:24.100Z</v>
+        <v>Pending</v>
+      </c>
+      <c r="H3">
+        <v>46199.399305555555</v>
+      </c>
+      <c r="I3">
+        <v>46199.399305555555</v>
       </c>
     </row>
     <row r="4">
@@ -1176,28 +998,28 @@
         <v>APP_0003</v>
       </c>
       <c r="B4" t="str">
-        <v>PAT_0004</v>
+        <v>PAT_0003</v>
       </c>
       <c r="C4" t="str">
         <v>DEN_0001</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-06-27</v>
+        <v>2026-06-28</v>
       </c>
       <c r="E4" t="str">
-        <v>22:32</v>
+        <v>15:10</v>
       </c>
       <c r="F4" t="str">
-        <v>1</v>
+        <v>Tooth Check</v>
       </c>
       <c r="G4" t="str">
         <v>Completed</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-06-27T17:02:48.748Z</v>
+        <v>2026-06-28T09:41:28.899Z</v>
       </c>
       <c r="I4" t="str">
-        <v>2026-06-27T17:11:03.621Z</v>
+        <v>2026-06-28T10:21:32.262Z</v>
       </c>
     </row>
     <row r="5">
@@ -1205,7 +1027,7 @@
         <v>APP_0004</v>
       </c>
       <c r="B5" t="str">
-        <v>PAT_0003</v>
+        <v>PAT_0005</v>
       </c>
       <c r="C5" t="str">
         <v>DEN_0001</v>
@@ -1214,19 +1036,19 @@
         <v>2026-06-28</v>
       </c>
       <c r="E5" t="str">
-        <v>22:42</v>
+        <v>15:12</v>
       </c>
       <c r="F5" t="str">
-        <v>Tooth Pain</v>
+        <v>Pain</v>
       </c>
       <c r="G5" t="str">
         <v>Completed</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-06-27T17:12:29.975Z</v>
+        <v>2026-06-28T09:42:25.340Z</v>
       </c>
       <c r="I5" t="str">
-        <v>2026-06-27T18:36:36.704Z</v>
+        <v>2026-06-28T10:20:46.834Z</v>
       </c>
     </row>
     <row r="6">
@@ -1234,28 +1056,28 @@
         <v>APP_0005</v>
       </c>
       <c r="B6" t="str">
-        <v>PAT_0001</v>
+        <v>PAT_0007</v>
       </c>
       <c r="C6" t="str">
         <v>DEN_0001</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-06-27</v>
+        <v>2026-06-28</v>
       </c>
       <c r="E6" t="str">
-        <v>23:12</v>
+        <v>15:12</v>
       </c>
       <c r="F6" t="str">
-        <v>1</v>
+        <v>TF</v>
       </c>
       <c r="G6" t="str">
         <v>Completed</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-06-27T17:42:15.935Z</v>
+        <v>2026-06-28T09:43:04.272Z</v>
       </c>
       <c r="I6" t="str">
-        <v>2026-06-27T18:17:27.235Z</v>
+        <v>2026-06-28T10:41:50.775Z</v>
       </c>
     </row>
     <row r="7">
@@ -1263,7 +1085,7 @@
         <v>APP_0006</v>
       </c>
       <c r="B7" t="str">
-        <v>PAT_0001</v>
+        <v>PAT_0017</v>
       </c>
       <c r="C7" t="str">
         <v>DEN_0001</v>
@@ -1272,19 +1094,19 @@
         <v>2026-06-28</v>
       </c>
       <c r="E7" t="str">
-        <v>00:03</v>
+        <v>15:13</v>
       </c>
       <c r="F7" t="str">
-        <v>Pain</v>
+        <v xml:space="preserve">Crown </v>
       </c>
       <c r="G7" t="str">
         <v>Completed</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-06-27T18:33:59.445Z</v>
+        <v>2026-06-28T09:44:08.410Z</v>
       </c>
       <c r="I7" t="str">
-        <v>2026-06-27T18:39:21.666Z</v>
+        <v>2026-06-28T10:20:36.771Z</v>
       </c>
     </row>
     <row r="8">
@@ -1292,7 +1114,7 @@
         <v>APP_0007</v>
       </c>
       <c r="B8" t="str">
-        <v>PAT_0005</v>
+        <v>PAT_0004</v>
       </c>
       <c r="C8" t="str">
         <v>DEN_0001</v>
@@ -1301,19 +1123,19 @@
         <v>2026-06-28</v>
       </c>
       <c r="E8" t="str">
-        <v>00:04</v>
+        <v>15:51</v>
       </c>
       <c r="F8" t="str">
-        <v>Tooth Pain</v>
+        <v>Tooth cavity</v>
       </c>
       <c r="G8" t="str">
         <v>Completed</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-06-27T18:35:03.256Z</v>
+        <v>2026-06-28T10:21:18.070Z</v>
       </c>
       <c r="I8" t="str">
-        <v>2026-06-27T18:39:45.194Z</v>
+        <v>2026-06-28T10:26:25.309Z</v>
       </c>
     </row>
     <row r="9">
@@ -1321,28 +1143,28 @@
         <v>APP_0008</v>
       </c>
       <c r="B9" t="str">
-        <v>PAT_0005</v>
+        <v>PAT_0012</v>
       </c>
       <c r="C9" t="str">
-        <v>DEN_0002</v>
+        <v>DEN_0001</v>
       </c>
       <c r="D9" t="str">
         <v>2026-06-28</v>
       </c>
       <c r="E9" t="str">
-        <v>00:05</v>
+        <v>15:57</v>
       </c>
       <c r="F9" t="str">
-        <v>Tooth Pain</v>
+        <v>Alignment issue</v>
       </c>
       <c r="G9" t="str">
         <v>Completed</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-06-27T18:36:08.831Z</v>
+        <v>2026-06-28T10:28:06.999Z</v>
       </c>
       <c r="I9" t="str">
-        <v>2026-06-27T18:40:55.318Z</v>
+        <v>2026-06-28T10:39:51.229Z</v>
       </c>
     </row>
     <row r="10">
@@ -1350,28 +1172,28 @@
         <v>APP_0009</v>
       </c>
       <c r="B10" t="str">
-        <v>PAT_0009</v>
+        <v>PAT_0015</v>
       </c>
       <c r="C10" t="str">
-        <v>DEN_0002</v>
+        <v>DEN_0001</v>
       </c>
       <c r="D10" t="str">
         <v>2026-06-28</v>
       </c>
       <c r="E10" t="str">
-        <v>00:06</v>
+        <v>16:01</v>
       </c>
       <c r="F10" t="str">
-        <v>Tooth Pain</v>
+        <v>123</v>
       </c>
       <c r="G10" t="str">
-        <v>Confirmed</v>
+        <v>Completed</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-06-27T18:36:21.089Z</v>
+        <v>2026-06-28T10:31:53.470Z</v>
       </c>
       <c r="I10" t="str">
-        <v>2026-06-27T18:41:15.647Z</v>
+        <v>2026-06-28T10:44:35.361Z</v>
       </c>
     </row>
     <row r="11">
@@ -1379,7 +1201,7 @@
         <v>APP_0010</v>
       </c>
       <c r="B11" t="str">
-        <v>PAT_0001</v>
+        <v>PAT_0004</v>
       </c>
       <c r="C11" t="str">
         <v>DEN_0001</v>
@@ -1388,31 +1210,437 @@
         <v>2026-06-28</v>
       </c>
       <c r="E11" t="str">
-        <v>00:15</v>
+        <v>16:01</v>
       </c>
       <c r="F11" t="str">
-        <v>4</v>
+        <v>16532</v>
       </c>
       <c r="G11" t="str">
-        <v>Treatment Done</v>
+        <v>Completed</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-06-27T18:46:14.834Z</v>
+        <v>2026-06-28T10:32:05.902Z</v>
       </c>
       <c r="I11" t="str">
-        <v>2026-06-27T18:47:39.850Z</v>
+        <v>2026-06-28T10:48:55.379Z</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>APP_0011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>PAT_0002</v>
+      </c>
+      <c r="C12" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-06-28</v>
+      </c>
+      <c r="E12" t="str">
+        <v>16:16</v>
+      </c>
+      <c r="F12" t="str">
+        <v>k</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="H12" t="str">
+        <v>2026-06-28T10:46:55.400Z</v>
+      </c>
+      <c r="I12" t="str">
+        <v>2026-06-28T10:49:50.858Z</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>APP_0012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>PAT_0018</v>
+      </c>
+      <c r="C13" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-06-28</v>
+      </c>
+      <c r="E13" t="str">
+        <v>16:16</v>
+      </c>
+      <c r="F13" t="str">
+        <v>k</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Confirmed</v>
+      </c>
+      <c r="H13" t="str">
+        <v>2026-06-28T10:47:11.986Z</v>
+      </c>
+      <c r="I13" t="str">
+        <v>2026-06-28T10:47:38.135Z</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>APP_0013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>PAT_0020</v>
+      </c>
+      <c r="C14" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-06-28</v>
+      </c>
+      <c r="E14" t="str">
+        <v>16:17</v>
+      </c>
+      <c r="F14" t="str">
+        <v>123</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Cancelled</v>
+      </c>
+      <c r="H14" t="str">
+        <v>2026-06-28T10:48:05.263Z</v>
+      </c>
+      <c r="I14" t="str">
+        <v>2026-06-29T03:38:38.446Z</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>APP_0014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>PAT_0001</v>
+      </c>
+      <c r="C15" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="E15" t="str">
+        <v>20:00</v>
+      </c>
+      <c r="F15" t="str">
+        <v>123</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="H15" t="str">
+        <v>2026-06-29T03:34:12.783Z</v>
+      </c>
+      <c r="I15" t="str">
+        <v>2026-06-29T03:40:50.095Z</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>APP_0015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>PAT_0001</v>
+      </c>
+      <c r="C16" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="E16" t="str">
+        <v>09:04</v>
+      </c>
+      <c r="F16" t="str">
+        <v>x</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Cancelled</v>
+      </c>
+      <c r="H16" t="str">
+        <v>2026-06-29T03:35:04.429Z</v>
+      </c>
+      <c r="I16" t="str">
+        <v>2026-06-29T03:41:19.794Z</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>APP_0016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>PAT_0001</v>
+      </c>
+      <c r="C17" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-06-26</v>
+      </c>
+      <c r="E17" t="str">
+        <v>09:05</v>
+      </c>
+      <c r="F17" t="str">
+        <v xml:space="preserve">c </v>
+      </c>
+      <c r="G17" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="H17" t="str">
+        <v>2026-06-29T03:35:41.783Z</v>
+      </c>
+      <c r="I17" t="str">
+        <v>2026-06-29T03:35:41.783Z</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>APP_0017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>PAT_0004</v>
+      </c>
+      <c r="C18" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="E18" t="str">
+        <v>09:06</v>
+      </c>
+      <c r="F18" t="str">
+        <v>hji</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Cancelled</v>
+      </c>
+      <c r="H18" t="str">
+        <v>2026-06-29T03:36:34.617Z</v>
+      </c>
+      <c r="I18" t="str">
+        <v>2026-06-29T03:42:41.693Z</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>APP_0018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>PAT_0002</v>
+      </c>
+      <c r="C19" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="E19" t="str">
+        <v>09:06</v>
+      </c>
+      <c r="F19" t="str">
+        <v>5t</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="H19" t="str">
+        <v>2026-06-29T03:37:00.221Z</v>
+      </c>
+      <c r="I19" t="str">
+        <v>2026-06-29T03:40:46.672Z</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>APP_0019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>PAT_0003</v>
+      </c>
+      <c r="C20" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="E20" t="str">
+        <v>09:07</v>
+      </c>
+      <c r="F20" t="str">
+        <v>sdf</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="H20" t="str">
+        <v>2026-06-29T03:37:50.378Z</v>
+      </c>
+      <c r="I20" t="str">
+        <v>2026-06-29T03:37:50.378Z</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>APP_0020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>PAT_0002</v>
+      </c>
+      <c r="C21" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="D21" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="E21" t="str">
+        <v>09:09</v>
+      </c>
+      <c r="F21" t="str">
+        <v>5</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="H21" t="str">
+        <v>2026-06-29T03:39:47.332Z</v>
+      </c>
+      <c r="I21" t="str">
+        <v>2026-06-29T03:40:49.092Z</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>APP_0021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>PAT_0001</v>
+      </c>
+      <c r="C22" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="D22" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="E22" t="str">
+        <v>10:15</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Tooth Visit</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="H22" t="str">
+        <v>2026-07-02T04:46:43.309Z</v>
+      </c>
+      <c r="I22" t="str">
+        <v>2026-07-02T05:04:47.841Z</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>APP_0022</v>
+      </c>
+      <c r="B23" t="str">
+        <v>PAT_0002</v>
+      </c>
+      <c r="C23" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="D23" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="E23" t="str">
+        <v>10:18</v>
+      </c>
+      <c r="F23" t="str">
+        <v>sdfghjkl</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Checked In</v>
+      </c>
+      <c r="H23" t="str">
+        <v>2026-07-02T04:49:03.710Z</v>
+      </c>
+      <c r="I23" t="str">
+        <v>2026-07-02T04:57:14.731Z</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>APP_0023</v>
+      </c>
+      <c r="B24" t="str">
+        <v>PAT_0003</v>
+      </c>
+      <c r="C24" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="D24" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="E24" t="str">
+        <v>10:19</v>
+      </c>
+      <c r="F24" t="str">
+        <v>wsaa</v>
+      </c>
+      <c r="G24" t="str">
+        <v>In Treatment</v>
+      </c>
+      <c r="H24" t="str">
+        <v>2026-07-02T04:50:01.080Z</v>
+      </c>
+      <c r="I24" t="str">
+        <v>2026-07-02T05:05:21.412Z</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>APP_0024</v>
+      </c>
+      <c r="B25" t="str">
+        <v>PAT_0016</v>
+      </c>
+      <c r="C25" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="D25" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="E25" t="str">
+        <v>10:23</v>
+      </c>
+      <c r="F25" t="str">
+        <v>asdasdasd</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Checked In</v>
+      </c>
+      <c r="H25" t="str">
+        <v>2026-07-02T04:56:48.991Z</v>
+      </c>
+      <c r="I25" t="str">
+        <v>2026-07-02T05:03:12.285Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I25"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1454,7 +1682,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TRT_c249ed60</v>
+        <v>TRT_0001</v>
       </c>
       <c r="B2" t="str">
         <v>PAT_0001</v>
@@ -1466,230 +1694,458 @@
         <v>DEN_0001</v>
       </c>
       <c r="E2" t="str">
-        <v>a</v>
+        <v>Tooth cavity</v>
       </c>
       <c r="F2" t="str">
-        <v>a</v>
+        <v>Dental filling</v>
       </c>
       <c r="G2" t="str">
-        <v>a</v>
+        <v>Painkiller for 3 days</v>
       </c>
       <c r="H2" t="str">
-        <v>a</v>
+        <v>Avoid cold drinks</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>2026-07-03</v>
       </c>
       <c r="J2" t="str">
-        <v>2026-06-27</v>
-      </c>
-      <c r="K2" t="str">
-        <v>2026-06-27T17:06:49.047Z</v>
-      </c>
-      <c r="L2" t="str">
-        <v>2026-06-27T17:06:49.047Z</v>
+        <v>2026-06-26</v>
+      </c>
+      <c r="K2">
+        <v>46199.447916666664</v>
+      </c>
+      <c r="L2">
+        <v>46199.447916666664</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TRT_2e3d5ae2</v>
+        <v>TRT_0002</v>
       </c>
       <c r="B3" t="str">
-        <v>PAT_0004</v>
+        <v>PAT_0002</v>
       </c>
       <c r="C3" t="str">
-        <v>APP_0003</v>
+        <v>APP_0002</v>
       </c>
       <c r="D3" t="str">
-        <v>DEN_0001</v>
+        <v>DEN_0002</v>
       </c>
       <c r="E3" t="str">
-        <v>dental cavity issue</v>
+        <v>Teeth alignment issue</v>
       </c>
       <c r="F3" t="str">
-        <v>T/F done</v>
+        <v>Consultation</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Follow-up optional</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>2026-07-05</v>
       </c>
       <c r="J3" t="str">
-        <v>2026-06-27</v>
-      </c>
-      <c r="K3" t="str">
-        <v>2026-06-27T17:10:38.620Z</v>
-      </c>
-      <c r="L3" t="str">
-        <v>2026-06-27T17:10:38.620Z</v>
+        <v>2026-06-26</v>
+      </c>
+      <c r="K3">
+        <v>46199.479166666664</v>
+      </c>
+      <c r="L3">
+        <v>46199.479166666664</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TRT_c8d8cdde</v>
+        <v>TRT_5864f4c8</v>
       </c>
       <c r="B4" t="str">
-        <v>PAT_0001</v>
+        <v>PAT_0003</v>
       </c>
       <c r="C4" t="str">
-        <v>APP_0005</v>
+        <v>APP_0003</v>
       </c>
       <c r="D4" t="str">
         <v>DEN_0001</v>
       </c>
       <c r="E4" t="str">
-        <v>1</v>
+        <v>d</v>
       </c>
       <c r="F4" t="str">
-        <v>1</v>
+        <v>d</v>
       </c>
       <c r="G4" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>11</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>2026-06-30</v>
       </c>
       <c r="J4" t="str">
-        <v>2026-06-27</v>
+        <v>2026-06-28</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-06-27T18:17:15.418Z</v>
+        <v>2026-06-28T09:48:52.491Z</v>
       </c>
       <c r="L4" t="str">
-        <v>2026-06-27T18:17:15.418Z</v>
+        <v>2026-06-28T09:48:52.491Z</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TRT_17d5c182</v>
+        <v>TRT_f73527fc</v>
       </c>
       <c r="B5" t="str">
-        <v>PAT_0001</v>
+        <v>PAT_0005</v>
       </c>
       <c r="C5" t="str">
-        <v>APP_0006</v>
+        <v>APP_0004</v>
       </c>
       <c r="D5" t="str">
         <v>DEN_0001</v>
       </c>
       <c r="E5" t="str">
-        <v>Treatment Performed</v>
+        <v>aa</v>
       </c>
       <c r="F5" t="str">
-        <v>Treatment Performed</v>
+        <v>aaa</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>aaa</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>aaa</v>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="J5" t="str">
         <v>2026-06-28</v>
       </c>
       <c r="K5" t="str">
-        <v>2026-06-27T18:38:27.161Z</v>
+        <v>2026-06-28T10:00:31.553Z</v>
       </c>
       <c r="L5" t="str">
-        <v>2026-06-27T18:38:27.161Z</v>
+        <v>2026-06-28T10:00:31.553Z</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>TRT_5d5cf4c8</v>
+        <v>TRT_c9116609</v>
       </c>
       <c r="B6" t="str">
-        <v>PAT_0005</v>
+        <v>PAT_0007</v>
       </c>
       <c r="C6" t="str">
-        <v>APP_0008</v>
+        <v>APP_0005</v>
       </c>
       <c r="D6" t="str">
-        <v>DEN_0002</v>
+        <v>DEN_0001</v>
       </c>
       <c r="E6" t="str">
-        <v>Treatment Performed</v>
+        <v>Tooth cavity</v>
       </c>
       <c r="F6" t="str">
-        <v>Treatment Performed</v>
+        <v>Dental filling</v>
       </c>
       <c r="G6" t="str">
-        <v>Treatment Performed</v>
+        <v xml:space="preserve">Painkiller for 3 days	</v>
       </c>
       <c r="H6" t="str">
-        <v>Treatment Performed</v>
+        <v>Avoid cold drinks</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>2026-06-30</v>
       </c>
       <c r="J6" t="str">
-        <v>2026-06-27</v>
+        <v>2026-06-28</v>
       </c>
       <c r="K6" t="str">
-        <v>2026-06-27T18:40:21.382Z</v>
+        <v>2026-06-28T10:17:05.173Z</v>
       </c>
       <c r="L6" t="str">
-        <v>2026-06-27T18:40:21.382Z</v>
+        <v>2026-06-28T10:17:05.173Z</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>TRT_c3961db9</v>
+        <v>TRT_025e4893</v>
       </c>
       <c r="B7" t="str">
+        <v>PAT_0004</v>
+      </c>
+      <c r="C7" t="str">
+        <v>APP_0007</v>
+      </c>
+      <c r="D7" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="E7" t="str">
+        <v>x</v>
+      </c>
+      <c r="F7" t="str">
+        <v>x</v>
+      </c>
+      <c r="G7" t="str">
+        <v>x</v>
+      </c>
+      <c r="H7" t="str">
+        <v>x</v>
+      </c>
+      <c r="I7" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="J7" t="str">
+        <v>2026-06-28</v>
+      </c>
+      <c r="K7" t="str">
+        <v>2026-06-28T10:22:16.787Z</v>
+      </c>
+      <c r="L7" t="str">
+        <v>2026-06-28T10:22:16.787Z</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>TRT_89693a7b</v>
+      </c>
+      <c r="B8" t="str">
+        <v>PAT_0012</v>
+      </c>
+      <c r="C8" t="str">
+        <v>APP_0008</v>
+      </c>
+      <c r="D8" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="E8" t="str">
+        <v>d</v>
+      </c>
+      <c r="F8" t="str">
+        <v>s</v>
+      </c>
+      <c r="G8" t="str">
+        <v>d</v>
+      </c>
+      <c r="H8" t="str">
+        <v>asdasd</v>
+      </c>
+      <c r="I8" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="J8" t="str">
+        <v>2026-06-28</v>
+      </c>
+      <c r="K8" t="str">
+        <v>2026-06-28T10:33:46.100Z</v>
+      </c>
+      <c r="L8" t="str">
+        <v>2026-06-28T10:33:46.100Z</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>TRT_f75020c9</v>
+      </c>
+      <c r="B9" t="str">
+        <v>PAT_0015</v>
+      </c>
+      <c r="C9" t="str">
+        <v>APP_0009</v>
+      </c>
+      <c r="D9" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="E9" t="str">
+        <v>asd</v>
+      </c>
+      <c r="F9" t="str">
+        <v>asd</v>
+      </c>
+      <c r="G9" t="str">
+        <v>sda</v>
+      </c>
+      <c r="H9" t="str">
+        <v>sda</v>
+      </c>
+      <c r="I9" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="J9" t="str">
+        <v>2026-06-28</v>
+      </c>
+      <c r="K9" t="str">
+        <v>2026-06-28T10:43:09.070Z</v>
+      </c>
+      <c r="L9" t="str">
+        <v>2026-06-28T10:43:09.070Z</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>TRT_ddf5aa89</v>
+      </c>
+      <c r="B10" t="str">
+        <v>PAT_0004</v>
+      </c>
+      <c r="C10" t="str">
+        <v>APP_0010</v>
+      </c>
+      <c r="D10" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="E10" t="str">
+        <v>123123</v>
+      </c>
+      <c r="F10" t="str">
+        <v>123123</v>
+      </c>
+      <c r="G10" t="str">
+        <v>222</v>
+      </c>
+      <c r="H10" t="str">
+        <v>2222</v>
+      </c>
+      <c r="I10" t="str">
+        <v>2026-07-01</v>
+      </c>
+      <c r="J10" t="str">
+        <v>2026-06-28</v>
+      </c>
+      <c r="K10" t="str">
+        <v>2026-06-28T10:45:19.861Z</v>
+      </c>
+      <c r="L10" t="str">
+        <v>2026-06-28T10:45:19.861Z</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>TRT_df4d13a6</v>
+      </c>
+      <c r="B11" t="str">
+        <v>PAT_0002</v>
+      </c>
+      <c r="C11" t="str">
+        <v>APP_0011</v>
+      </c>
+      <c r="D11" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="E11" t="str">
+        <v>123</v>
+      </c>
+      <c r="F11" t="str">
+        <v>321312</v>
+      </c>
+      <c r="G11" t="str">
+        <v>222</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="J11" t="str">
+        <v>2026-06-28</v>
+      </c>
+      <c r="K11" t="str">
+        <v>2026-06-28T10:49:38.947Z</v>
+      </c>
+      <c r="L11" t="str">
+        <v>2026-06-28T10:49:38.947Z</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>TRT_ff430400</v>
+      </c>
+      <c r="B12" t="str">
+        <v>PAT_0020</v>
+      </c>
+      <c r="C12" t="str">
+        <v>APP_0013</v>
+      </c>
+      <c r="D12" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="E12" t="str">
+        <v>2</v>
+      </c>
+      <c r="F12" t="str">
+        <v>2</v>
+      </c>
+      <c r="G12" t="str">
+        <v>2</v>
+      </c>
+      <c r="H12" t="str">
+        <v>2</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="K12" t="str">
+        <v>2026-06-29T03:29:27.749Z</v>
+      </c>
+      <c r="L12" t="str">
+        <v>2026-06-29T03:29:27.749Z</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>TRT_559de661</v>
+      </c>
+      <c r="B13" t="str">
         <v>PAT_0001</v>
       </c>
-      <c r="C7" t="str">
-        <v>APP_0010</v>
-      </c>
-      <c r="D7" t="str">
-        <v>DEN_0001</v>
-      </c>
-      <c r="E7" t="str">
-        <v>sss</v>
-      </c>
-      <c r="F7" t="str">
+      <c r="C13" t="str">
+        <v>APP_0021</v>
+      </c>
+      <c r="D13" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="E13" t="str">
         <v>s</v>
       </c>
-      <c r="G7" t="str">
+      <c r="F13" t="str">
+        <v>s</v>
+      </c>
+      <c r="G13" t="str">
         <v/>
       </c>
-      <c r="H7" t="str">
+      <c r="H13" t="str">
         <v/>
       </c>
-      <c r="I7" t="str">
-        <v>2026-06-30</v>
-      </c>
-      <c r="J7" t="str">
-        <v>2026-06-27</v>
-      </c>
-      <c r="K7" t="str">
-        <v>2026-06-27T18:47:39.755Z</v>
-      </c>
-      <c r="L7" t="str">
-        <v>2026-06-27T18:47:39.755Z</v>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="K13" t="str">
+        <v>2026-07-02T05:04:31.812Z</v>
+      </c>
+      <c r="L13" t="str">
+        <v>2026-07-02T05:04:31.813Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1728,95 +2184,95 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>PAY_20a25a4b</v>
+        <v>PAY_0001</v>
       </c>
       <c r="B2" t="str">
         <v>PAT_0001</v>
       </c>
       <c r="C2" t="str">
-        <v>TRT_c249ed60</v>
+        <v>TRT_0001</v>
       </c>
       <c r="D2">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="E2">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="F2" t="str">
         <v>Cash</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-06-27</v>
+        <v>2026-06-26</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>REC-001</v>
       </c>
       <c r="I2" t="str">
-        <v>Partial</v>
-      </c>
-      <c r="J2" t="str">
-        <v>2026-06-27T17:07:12.460Z</v>
-      </c>
-      <c r="K2" t="str">
-        <v>2026-06-27T17:07:12.460Z</v>
+        <v>Paid</v>
+      </c>
+      <c r="J2">
+        <v>46199.458333333336</v>
+      </c>
+      <c r="K2">
+        <v>46199.458333333336</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>PAY_fa17a27b</v>
+        <v>PAY_0002</v>
       </c>
       <c r="B3" t="str">
-        <v>PAT_0004</v>
+        <v>PAT_0002</v>
       </c>
       <c r="C3" t="str">
-        <v>TRT_2e3d5ae2</v>
+        <v>TRT_0002</v>
       </c>
       <c r="D3">
-        <v>500</v>
+        <v>3000</v>
       </c>
       <c r="E3">
-        <v>500</v>
+        <v>3000</v>
       </c>
       <c r="F3" t="str">
-        <v>Cash</v>
+        <v>Card</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-06-27</v>
+        <v>2026-06-26</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>REC-002</v>
       </c>
       <c r="I3" t="str">
         <v>Paid</v>
       </c>
-      <c r="J3" t="str">
-        <v>2026-06-27T17:10:57.889Z</v>
-      </c>
-      <c r="K3" t="str">
-        <v>2026-06-27T17:10:57.889Z</v>
+      <c r="J3">
+        <v>46199.489583333336</v>
+      </c>
+      <c r="K3">
+        <v>46199.489583333336</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>PAY_2cc07281</v>
+        <v>PAY_5675099e</v>
       </c>
       <c r="B4" t="str">
-        <v>PAT_0001</v>
+        <v>PAT_0007</v>
       </c>
       <c r="C4" t="str">
-        <v>TRT_17d5c182</v>
+        <v>TRT_c9116609</v>
       </c>
       <c r="D4">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="E4">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="F4" t="str">
         <v>Cash</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-06-27</v>
+        <v>2026-06-28</v>
       </c>
       <c r="H4" t="str">
         <v/>
@@ -1825,33 +2281,33 @@
         <v>Paid</v>
       </c>
       <c r="J4" t="str">
-        <v>2026-06-27T18:39:17.710Z</v>
+        <v>2026-06-28T10:18:24.621Z</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-06-27T18:39:17.710Z</v>
+        <v>2026-06-28T10:18:24.621Z</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>PAY_f28ec9e6</v>
+        <v>PAY_b3ffc7bc</v>
       </c>
       <c r="B5" t="str">
-        <v>PAT_0005</v>
+        <v>PAT_0004</v>
       </c>
       <c r="C5" t="str">
-        <v>TRT_5d5cf4c8</v>
+        <v>TRT_025e4893</v>
       </c>
       <c r="D5">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="E5">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="F5" t="str">
         <v>Cash</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-06-27</v>
+        <v>2026-06-28</v>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -1860,15 +2316,295 @@
         <v>Paid</v>
       </c>
       <c r="J5" t="str">
-        <v>2026-06-27T18:40:48.220Z</v>
+        <v>2026-06-28T10:26:23.385Z</v>
       </c>
       <c r="K5" t="str">
-        <v>2026-06-27T18:40:48.220Z</v>
+        <v>2026-06-28T10:26:23.385Z</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>PAY_0387cd92</v>
+      </c>
+      <c r="B6" t="str">
+        <v>PAT_0012</v>
+      </c>
+      <c r="C6" t="str">
+        <v>TRT_89693a7b</v>
+      </c>
+      <c r="D6">
+        <v>500</v>
+      </c>
+      <c r="E6">
+        <v>200</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Cash</v>
+      </c>
+      <c r="G6" t="str">
+        <v>2026-06-28</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="J6" t="str">
+        <v>2026-06-28T10:36:49.879Z</v>
+      </c>
+      <c r="K6" t="str">
+        <v>2026-06-28T10:36:49.879Z</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>PAY_592f1171</v>
+      </c>
+      <c r="B7" t="str">
+        <v>PAT_0012</v>
+      </c>
+      <c r="C7" t="str">
+        <v>TRT_89693a7b</v>
+      </c>
+      <c r="D7">
+        <v>12312</v>
+      </c>
+      <c r="E7">
+        <v>3333</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Cash</v>
+      </c>
+      <c r="G7" t="str">
+        <v>2026-06-28</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="J7" t="str">
+        <v>2026-06-28T10:39:03.697Z</v>
+      </c>
+      <c r="K7" t="str">
+        <v>2026-06-28T10:39:03.697Z</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>PAY_2d4c231e</v>
+      </c>
+      <c r="B8" t="str">
+        <v>PAT_0007</v>
+      </c>
+      <c r="C8" t="str">
+        <v>TRT_c9116609</v>
+      </c>
+      <c r="D8">
+        <v>154</v>
+      </c>
+      <c r="E8">
+        <v>58</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Cash</v>
+      </c>
+      <c r="G8" t="str">
+        <v>2026-06-28</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="J8" t="str">
+        <v>2026-06-28T10:41:45.239Z</v>
+      </c>
+      <c r="K8" t="str">
+        <v>2026-06-28T10:41:45.239Z</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>PAY_6b854c30</v>
+      </c>
+      <c r="B9" t="str">
+        <v>PAT_0015</v>
+      </c>
+      <c r="C9" t="str">
+        <v>TRT_f75020c9</v>
+      </c>
+      <c r="D9">
+        <v>1500</v>
+      </c>
+      <c r="E9">
+        <v>500</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Cash</v>
+      </c>
+      <c r="G9" t="str">
+        <v>2026-06-28</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="J9" t="str">
+        <v>2026-06-28T10:44:31.390Z</v>
+      </c>
+      <c r="K9" t="str">
+        <v>2026-06-28T10:44:31.390Z</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>PAY_44aa1454</v>
+      </c>
+      <c r="B10" t="str">
+        <v>PAT_0004</v>
+      </c>
+      <c r="C10" t="str">
+        <v>TRT_ddf5aa89</v>
+      </c>
+      <c r="D10">
+        <v>15</v>
+      </c>
+      <c r="E10">
+        <v>15</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Cash</v>
+      </c>
+      <c r="G10" t="str">
+        <v>2026-06-28</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="J10" t="str">
+        <v>2026-06-28T10:48:53.690Z</v>
+      </c>
+      <c r="K10" t="str">
+        <v>2026-06-28T10:48:53.690Z</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>PAY_b142300a</v>
+      </c>
+      <c r="B11" t="str">
+        <v>PAT_0002</v>
+      </c>
+      <c r="C11" t="str">
+        <v>TRT_df4d13a6</v>
+      </c>
+      <c r="D11">
+        <v>500</v>
+      </c>
+      <c r="E11">
+        <v>500</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Cash</v>
+      </c>
+      <c r="G11" t="str">
+        <v>2026-06-28</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="J11" t="str">
+        <v>2026-06-28T10:49:48.344Z</v>
+      </c>
+      <c r="K11" t="str">
+        <v>2026-06-28T10:49:48.344Z</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>PAY_fadfa41b</v>
+      </c>
+      <c r="B12" t="str">
+        <v>PAT_0020</v>
+      </c>
+      <c r="C12" t="str">
+        <v>TRT_ff430400</v>
+      </c>
+      <c r="D12">
+        <v>123</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Cash</v>
+      </c>
+      <c r="G12" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="J12" t="str">
+        <v>2026-06-29T03:29:39.996Z</v>
+      </c>
+      <c r="K12" t="str">
+        <v>2026-06-29T03:29:39.996Z</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>PAY_b054eb79</v>
+      </c>
+      <c r="B13" t="str">
+        <v>PAT_0001</v>
+      </c>
+      <c r="C13" t="str">
+        <v>TRT_559de661</v>
+      </c>
+      <c r="D13">
+        <v>1111111</v>
+      </c>
+      <c r="E13">
+        <v>11111111</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Cash</v>
+      </c>
+      <c r="G13" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="J13" t="str">
+        <v>2026-07-02T05:04:45.522Z</v>
+      </c>
+      <c r="K13" t="str">
+        <v>2026-07-02T05:04:45.522Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1881,15 +2617,6 @@
       <c r="A1" t="str">
         <v>Dental Clinic Simple Test Excel</v>
       </c>
-      <c r="B1" t="str">
-        <v/>
-      </c>
-      <c r="C1" t="str">
-        <v/>
-      </c>
-      <c r="D1" t="str">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
